--- a/AAII_Financials/Yearly/BPOP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BPOP_YR_FIN.xlsx
@@ -2218,13 +2218,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4680200</v>
+        <v>4680800</v>
       </c>
       <c r="E42" s="3">
-        <v>6429300</v>
+        <v>6430000</v>
       </c>
       <c r="F42" s="3">
-        <v>7047600</v>
+        <v>7047700</v>
       </c>
       <c r="G42" s="3">
         <v>5654700</v>
@@ -2371,13 +2371,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>301400</v>
+        <v>300800</v>
       </c>
       <c r="E45" s="3">
-        <v>264000</v>
+        <v>263400</v>
       </c>
       <c r="F45" s="3">
-        <v>263500</v>
+        <v>263400</v>
       </c>
       <c r="G45" s="3">
         <v>240400</v>
